--- a/output/基础户有效户数量以及增量情况.xlsx
+++ b/output/基础户有效户数量以及增量情况.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,177 +432,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧时点</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧基础户标识</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>旧有效户标识</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>新基础户标识</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>新有效户标识</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>账户销户</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_标识</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_标识</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_年日均</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_年日均</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_标识</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_标识</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_年日均</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_年日均</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>预计年日均</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>预警基础户</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>预警有效户</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>基础户临界</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>有效户临界</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户达标</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户达标</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户保持</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户保持</t>
         </is>
@@ -69142,37 +69154,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>基础户增量</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>有效户增量</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧基础户数量</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新基础户数量</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧有效户数量</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新有效户数量</t>
         </is>
@@ -69418,37 +69430,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>基础户增量</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>有效户增量</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧基础户数量</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新基础户数量</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧有效户数量</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新有效户数量</t>
         </is>
@@ -69694,37 +69706,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>基础户增量</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>有效户增量</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧基础户数量</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新基础户数量</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧有效户数量</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新有效户数量</t>
         </is>

--- a/output/基础户有效户数量以及增量情况.xlsx
+++ b/output/基础户有效户数量以及增量情况.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>刘羽佳</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -17618,7 +17618,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -23824,7 +23824,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -24252,7 +24252,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -25643,7 +25643,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -26927,7 +26927,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28518,7 +28518,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -29374,7 +29374,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -32156,7 +32156,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -32584,7 +32584,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -35901,7 +35901,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -36008,7 +36008,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -36329,7 +36329,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -40395,7 +40395,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -40502,7 +40502,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -41893,7 +41893,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -42949,7 +42949,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -43270,7 +43270,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -43377,7 +43377,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -44019,7 +44019,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -45503,7 +45503,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -45717,7 +45717,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -45824,7 +45824,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -46145,7 +46145,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -46252,7 +46252,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -46359,7 +46359,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -46894,7 +46894,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -47964,7 +47964,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -48499,7 +48499,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -48927,7 +48927,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -49997,7 +49997,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -50104,7 +50104,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -50425,7 +50425,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -50639,7 +50639,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -50853,7 +50853,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -51602,7 +51602,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -51816,7 +51816,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -52030,7 +52030,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -52137,7 +52137,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -52351,7 +52351,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -53421,7 +53421,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -53528,7 +53528,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -53635,7 +53635,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -55026,7 +55026,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -55240,7 +55240,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -55347,7 +55347,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -56310,7 +56310,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -56524,7 +56524,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -57594,7 +57594,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D535" t="n">
@@ -57701,7 +57701,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -57808,7 +57808,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -58236,7 +58236,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -58557,7 +58557,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D544" t="n">
@@ -59627,7 +59627,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -59734,7 +59734,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -59841,7 +59841,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -59948,7 +59948,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D557" t="n">
@@ -60055,7 +60055,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D558" t="n">
@@ -60162,7 +60162,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -61018,7 +61018,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D567" t="n">
@@ -61767,7 +61767,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D574" t="n">
@@ -61874,7 +61874,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -63158,7 +63158,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D587" t="n">
@@ -63372,7 +63372,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D589" t="n">
@@ -63586,7 +63586,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D591" t="n">
@@ -64014,7 +64014,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D595" t="n">
@@ -64121,7 +64121,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D596" t="n">
@@ -65298,7 +65298,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D607" t="n">
@@ -67759,7 +67759,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D630" t="n">
@@ -69372,19 +69372,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-23</v>
+        <v>-40</v>
       </c>
       <c r="C9" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -69397,19 +69397,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -69548,7 +69548,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -69557,7 +69557,7 @@
         <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
@@ -69648,22 +69648,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -69673,22 +69673,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -69824,7 +69824,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -69833,7 +69833,7 @@
         <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
@@ -69924,22 +69924,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -69949,22 +69949,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
